--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92572356674</v>
+        <v>46157.93111494128</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93111494128</v>
+        <v>46157.93179157447</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93179157447</v>
+        <v>46157.9340382811</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9340382811</v>
+        <v>46157.93721899204</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93721899204</v>
+        <v>46158.28219769331</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219769331</v>
+        <v>46158.29695290178</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29695290178</v>
+        <v>46158.2981927144</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981927144</v>
+        <v>46158.33390874567</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33390874567</v>
+        <v>46158.36860670507</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/28. Сотрудники/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860670507</v>
+        <v>46158.37291317054</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
